--- a/5/search/FY2_Missile2_results/solutions_direction_351.0.xlsx
+++ b/5/search/FY2_Missile2_results/solutions_direction_351.0.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,500 +487,500 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>225</v>
+        <v>193.5</v>
       </c>
       <c r="B2" t="n">
-        <v>81.2</v>
+        <v>140</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
-        <v>11310.99515241183</v>
+        <v>8732.837067463806</v>
       </c>
       <c r="F2" t="n">
-        <v>710.995152411828</v>
+        <v>615.6235774441582</v>
       </c>
       <c r="G2" t="n">
         <v>1400</v>
       </c>
       <c r="H2" t="n">
-        <v>10966.49272861774</v>
+        <v>7235.387390051385</v>
       </c>
       <c r="I2" t="n">
-        <v>366.492728617742</v>
+        <v>256.117717106064</v>
       </c>
       <c r="J2" t="n">
-        <v>1223.6</v>
+        <v>807.0999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>3.300000000000001</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>225</v>
+        <v>211.5</v>
       </c>
       <c r="B3" t="n">
-        <v>100.8</v>
+        <v>106</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>11429.78909165117</v>
+        <v>10915.4417109416</v>
       </c>
       <c r="F3" t="n">
-        <v>829.7890916511682</v>
+        <v>735.3818256813132</v>
       </c>
       <c r="G3" t="n">
         <v>1400</v>
       </c>
       <c r="H3" t="n">
-        <v>11002.13091038954</v>
+        <v>10282.78270899086</v>
       </c>
       <c r="I3" t="n">
-        <v>402.1309103895443</v>
+        <v>347.6878906620793</v>
       </c>
       <c r="J3" t="n">
-        <v>1223.6</v>
+        <v>1159.9</v>
       </c>
       <c r="K3" t="n">
-        <v>1.700000000000001</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>225</v>
+        <v>211.5</v>
       </c>
       <c r="B4" t="n">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>11604.02020253553</v>
+        <v>10894.9783469971</v>
       </c>
       <c r="F4" t="n">
-        <v>1004.020202535533</v>
+        <v>722.8418601281305</v>
       </c>
       <c r="G4" t="n">
         <v>1400</v>
       </c>
       <c r="H4" t="n">
-        <v>11010.05050633883</v>
+        <v>10250.3823827454</v>
       </c>
       <c r="I4" t="n">
-        <v>410.0505063388335</v>
+        <v>327.8329452028733</v>
       </c>
       <c r="J4" t="n">
-        <v>1223.6</v>
+        <v>1159.9</v>
       </c>
       <c r="K4" t="n">
-        <v>2.600000000000001</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>234</v>
+        <v>211.5</v>
       </c>
       <c r="B5" t="n">
-        <v>75.59999999999999</v>
+        <v>132</v>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>11466.76121912027</v>
+        <v>11099.61198644208</v>
       </c>
       <c r="F5" t="n">
-        <v>666.0597827030479</v>
+        <v>848.2415156599582</v>
       </c>
       <c r="G5" t="n">
         <v>1400</v>
       </c>
       <c r="H5" t="n">
-        <v>11244.57839375371</v>
+        <v>10311.7724745789</v>
       </c>
       <c r="I5" t="n">
-        <v>360.2513588293178</v>
+        <v>365.4528418624216</v>
       </c>
       <c r="J5" t="n">
-        <v>1277.5</v>
+        <v>1159.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8999999999999986</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>234</v>
+        <v>211.5</v>
       </c>
       <c r="B6" t="n">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="C6" t="n">
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>11539.1763622027</v>
+        <v>11085.96974381241</v>
       </c>
       <c r="F6" t="n">
-        <v>765.7306764100413</v>
+        <v>839.881538624503</v>
       </c>
       <c r="G6" t="n">
         <v>1400</v>
       </c>
       <c r="H6" t="n">
-        <v>11251.16158857939</v>
+        <v>10286.19326964827</v>
       </c>
       <c r="I6" t="n">
-        <v>369.3123491663171</v>
+        <v>349.7778849209432</v>
       </c>
       <c r="J6" t="n">
-        <v>1277.5</v>
+        <v>1159.9</v>
       </c>
       <c r="K6" t="n">
-        <v>3.400000000000002</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>234</v>
+        <v>220.5</v>
       </c>
       <c r="B7" t="n">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>11670.84025871621</v>
+        <v>11306.50975937277</v>
       </c>
       <c r="F7" t="n">
-        <v>946.9504831500294</v>
+        <v>807.7033799228726</v>
       </c>
       <c r="G7" t="n">
         <v>1400</v>
       </c>
       <c r="H7" t="n">
-        <v>11259.39058211148</v>
+        <v>10786.39207890235</v>
       </c>
       <c r="I7" t="n">
-        <v>380.6385870875663</v>
+        <v>363.4809148650271</v>
       </c>
       <c r="J7" t="n">
-        <v>1277.5</v>
+        <v>1223.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.600000000000001</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>243</v>
+        <v>220.5</v>
       </c>
       <c r="B8" t="n">
-        <v>86.8</v>
+        <v>116</v>
       </c>
       <c r="C8" t="n">
         <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>11684.74899698086</v>
+        <v>11294.34326392317</v>
       </c>
       <c r="F8" t="n">
-        <v>781.2850696035974</v>
+        <v>797.3122111495896</v>
       </c>
       <c r="G8" t="n">
         <v>1400</v>
       </c>
       <c r="H8" t="n">
-        <v>11487.7171200939</v>
+        <v>10765.10071186555</v>
       </c>
       <c r="I8" t="n">
-        <v>394.5882381058458</v>
+        <v>345.2963695117819</v>
       </c>
       <c r="J8" t="n">
-        <v>1277.5</v>
+        <v>1223.6</v>
       </c>
       <c r="K8" t="n">
-        <v>2.599999999999998</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="B9" t="n">
-        <v>123.2</v>
+        <v>102</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>11776.27348172835</v>
+        <v>11423.00086655178</v>
       </c>
       <c r="F9" t="n">
-        <v>960.9119848799724</v>
+        <v>823.0008665517772</v>
       </c>
       <c r="G9" t="n">
         <v>1400</v>
       </c>
       <c r="H9" t="n">
-        <v>11496.61533388879</v>
+        <v>10990.25151646561</v>
       </c>
       <c r="I9" t="n">
-        <v>412.0519659799379</v>
+        <v>390.2515164656102</v>
       </c>
       <c r="J9" t="n">
-        <v>1277.5</v>
+        <v>1223.6</v>
       </c>
       <c r="K9" t="n">
-        <v>3.300000000000001</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="B10" t="n">
-        <v>89.59999999999999</v>
+        <v>140</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>11778.49661843204</v>
+        <v>11604.02020253553</v>
       </c>
       <c r="F10" t="n">
-        <v>718.282689119634</v>
+        <v>1004.020202535533</v>
       </c>
       <c r="G10" t="n">
         <v>1400</v>
       </c>
       <c r="H10" t="n">
-        <v>11667.74492764806</v>
+        <v>11010.05050633883</v>
       </c>
       <c r="I10" t="n">
-        <v>377.424033679451</v>
+        <v>410.0505063388335</v>
       </c>
       <c r="J10" t="n">
-        <v>1321.6</v>
+        <v>1223.6</v>
       </c>
       <c r="K10" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="B11" t="n">
-        <v>131.6</v>
+        <v>100</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>11837.33345416103</v>
+        <v>11529.77179816602</v>
       </c>
       <c r="F11" t="n">
-        <v>899.3638498222313</v>
+        <v>752.7864045000422</v>
       </c>
       <c r="G11" t="n">
         <v>1400</v>
       </c>
       <c r="H11" t="n">
-        <v>11674.66690832205</v>
+        <v>11235.87917201978</v>
       </c>
       <c r="I11" t="n">
-        <v>398.7276996444625</v>
+        <v>348.2779073125686</v>
       </c>
       <c r="J11" t="n">
-        <v>1321.6</v>
+        <v>1277.5</v>
       </c>
       <c r="K11" t="n">
-        <v>3.800000000000002</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>261</v>
+        <v>234</v>
       </c>
       <c r="B12" t="n">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>11894.87603949296</v>
+        <v>11675.54254073456</v>
       </c>
       <c r="F12" t="n">
-        <v>736.2734351200675</v>
+        <v>953.4226191050291</v>
       </c>
       <c r="G12" t="n">
         <v>1400</v>
       </c>
       <c r="H12" t="n">
-        <v>11842.31405923945</v>
+        <v>11269.97071665275</v>
       </c>
       <c r="I12" t="n">
-        <v>404.4101526801012</v>
+        <v>395.2008929863155</v>
       </c>
       <c r="J12" t="n">
-        <v>1321.6</v>
+        <v>1277.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>261</v>
+        <v>234</v>
       </c>
       <c r="B13" t="n">
-        <v>123.2</v>
+        <v>140</v>
       </c>
       <c r="C13" t="n">
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>11922.90909562817</v>
+        <v>11670.84025871621</v>
       </c>
       <c r="F13" t="n">
-        <v>913.2671857547161</v>
+        <v>946.9504831500294</v>
       </c>
       <c r="G13" t="n">
         <v>1400</v>
       </c>
       <c r="H13" t="n">
-        <v>11845.81819125635</v>
+        <v>11259.39058211148</v>
       </c>
       <c r="I13" t="n">
-        <v>426.5343715094323</v>
+        <v>380.6385870875663</v>
       </c>
       <c r="J13" t="n">
-        <v>1321.6</v>
+        <v>1277.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.699999999999999</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>270</v>
+        <v>238.5</v>
       </c>
       <c r="B14" t="n">
-        <v>81.2</v>
+        <v>130</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E14" t="n">
-        <v>12000</v>
+        <v>11728.30074634771</v>
       </c>
       <c r="F14" t="n">
-        <v>750.4</v>
+        <v>956.6271145358719</v>
       </c>
       <c r="G14" t="n">
         <v>1400</v>
       </c>
       <c r="H14" t="n">
-        <v>12000</v>
+        <v>11388.67667928234</v>
       </c>
       <c r="I14" t="n">
-        <v>425.6</v>
+        <v>402.4110077057119</v>
       </c>
       <c r="J14" t="n">
-        <v>1321.6</v>
+        <v>1277.5</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3000000000000007</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>270</v>
+        <v>243</v>
       </c>
       <c r="B15" t="n">
-        <v>92.40000000000001</v>
+        <v>122</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>12000</v>
+        <v>11778.4526361271</v>
       </c>
       <c r="F15" t="n">
-        <v>660.8</v>
+        <v>965.1888161960765</v>
       </c>
       <c r="G15" t="n">
         <v>1400</v>
       </c>
       <c r="H15" t="n">
-        <v>12000</v>
+        <v>11501.51843128598</v>
       </c>
       <c r="I15" t="n">
-        <v>383.5999999999999</v>
+        <v>421.6748364411721</v>
       </c>
       <c r="J15" t="n">
-        <v>1355.9</v>
+        <v>1277.5</v>
       </c>
       <c r="K15" t="n">
-        <v>3.100000000000001</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>270</v>
+        <v>247.5</v>
       </c>
       <c r="B16" t="n">
-        <v>120.4</v>
+        <v>136</v>
       </c>
       <c r="C16" t="n">
         <v>4</v>
@@ -989,655 +989,1390 @@
         <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>12000</v>
+        <v>11791.82021279339</v>
       </c>
       <c r="F16" t="n">
-        <v>918.4</v>
+        <v>897.4095343138599</v>
       </c>
       <c r="G16" t="n">
         <v>1400</v>
       </c>
       <c r="H16" t="n">
-        <v>12000</v>
+        <v>11583.64042558678</v>
       </c>
       <c r="I16" t="n">
-        <v>436.8</v>
+        <v>394.8190686277199</v>
       </c>
       <c r="J16" t="n">
         <v>1321.6</v>
       </c>
       <c r="K16" t="n">
-        <v>0.09999999999999964</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>270</v>
+        <v>247.5</v>
       </c>
       <c r="B17" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C17" t="n">
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>12000</v>
+        <v>11788.75874533447</v>
       </c>
       <c r="F17" t="n">
-        <v>840</v>
+        <v>890.0184980537697</v>
       </c>
       <c r="G17" t="n">
         <v>1400</v>
       </c>
       <c r="H17" t="n">
-        <v>12000</v>
+        <v>11577.51749066894</v>
       </c>
       <c r="I17" t="n">
-        <v>420</v>
+        <v>380.0369961075393</v>
       </c>
       <c r="J17" t="n">
-        <v>1355.9</v>
+        <v>1321.6</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>279</v>
+        <v>247.5</v>
       </c>
       <c r="B18" t="n">
-        <v>89.59999999999999</v>
+        <v>140</v>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>12112.13222454084</v>
+        <v>11785.69727787555</v>
       </c>
       <c r="F18" t="n">
-        <v>692.0249974614053</v>
+        <v>882.6274617936793</v>
       </c>
       <c r="G18" t="n">
         <v>1400</v>
       </c>
       <c r="H18" t="n">
-        <v>12154.18180874365</v>
+        <v>11571.3945557511</v>
       </c>
       <c r="I18" t="n">
-        <v>426.5343715094323</v>
+        <v>365.2549235873587</v>
       </c>
       <c r="J18" t="n">
-        <v>1355.9</v>
+        <v>1321.6</v>
       </c>
       <c r="K18" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="B19" t="n">
-        <v>100.8</v>
+        <v>130</v>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>11839.31116292503</v>
+      </c>
+      <c r="F19" t="n">
+        <v>905.4506115265201</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H19" t="n">
+        <v>11678.62232585005</v>
+      </c>
+      <c r="I19" t="n">
+        <v>410.9012230530403</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1321.6</v>
+      </c>
+      <c r="K19" t="n">
         <v>2</v>
-      </c>
-      <c r="E19" t="n">
-        <v>12126.14875260844</v>
-      </c>
-      <c r="F19" t="n">
-        <v>603.528122144081</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1400</v>
-      </c>
-      <c r="H19" t="n">
-        <v>12157.68594076055</v>
-      </c>
-      <c r="I19" t="n">
-        <v>404.4101526801012</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1380.4</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1.300000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="B20" t="n">
-        <v>103.6</v>
+        <v>132</v>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>12129.65288462534</v>
+        <v>11836.83902697003</v>
       </c>
       <c r="F20" t="n">
-        <v>581.4039033147499</v>
+        <v>897.8421593961589</v>
       </c>
       <c r="G20" t="n">
         <v>1400</v>
       </c>
       <c r="H20" t="n">
-        <v>12162.06610578168</v>
+        <v>11673.67805394006</v>
       </c>
       <c r="I20" t="n">
-        <v>376.7548791434373</v>
+        <v>395.6843187923178</v>
       </c>
       <c r="J20" t="n">
-        <v>1380.4</v>
+        <v>1321.6</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="B21" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C21" t="n">
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>12087.60330042253</v>
+        <v>11834.36689101503</v>
       </c>
       <c r="F21" t="n">
-        <v>846.8945292667229</v>
+        <v>890.2337072657976</v>
       </c>
       <c r="G21" t="n">
         <v>1400</v>
       </c>
       <c r="H21" t="n">
-        <v>12153.30577573943</v>
+        <v>11668.73378203006</v>
       </c>
       <c r="I21" t="n">
-        <v>432.065426216765</v>
+        <v>380.4674145315954</v>
       </c>
       <c r="J21" t="n">
-        <v>1355.9</v>
+        <v>1321.6</v>
       </c>
       <c r="K21" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>288</v>
+        <v>256.5</v>
       </c>
       <c r="B22" t="n">
-        <v>75.59999999999999</v>
+        <v>126</v>
       </c>
       <c r="C22" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E22" t="n">
-        <v>12280.34021729695</v>
+        <v>11882.34353661662</v>
       </c>
       <c r="F22" t="n">
-        <v>537.2015284170367</v>
+        <v>909.9255601195709</v>
       </c>
       <c r="G22" t="n">
         <v>1400</v>
       </c>
       <c r="H22" t="n">
-        <v>12327.06358684645</v>
+        <v>11764.68707323325</v>
       </c>
       <c r="I22" t="n">
-        <v>393.4017831532095</v>
+        <v>419.8511202391419</v>
       </c>
       <c r="J22" t="n">
-        <v>1380.4</v>
+        <v>1321.6</v>
       </c>
       <c r="K22" t="n">
-        <v>3.099999999999998</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>288</v>
+        <v>256.5</v>
       </c>
       <c r="B23" t="n">
-        <v>81.2</v>
+        <v>128</v>
       </c>
       <c r="C23" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E23" t="n">
-        <v>12301.10615931895</v>
+        <v>11880.47597370578</v>
       </c>
       <c r="F23" t="n">
-        <v>473.2905305220022</v>
+        <v>902.1466007563895</v>
       </c>
       <c r="G23" t="n">
         <v>1400</v>
       </c>
       <c r="H23" t="n">
-        <v>12326.19833926219</v>
+        <v>11760.95194741155</v>
       </c>
       <c r="I23" t="n">
-        <v>396.0647413988357</v>
+        <v>404.293201512779</v>
       </c>
       <c r="J23" t="n">
-        <v>1395.1</v>
+        <v>1321.6</v>
       </c>
       <c r="K23" t="n">
-        <v>1.899999999999999</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="B24" t="n">
-        <v>92.40000000000001</v>
+        <v>124</v>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E24" t="n">
-        <v>12228.42536224196</v>
+        <v>11922.40850534004</v>
       </c>
       <c r="F24" t="n">
-        <v>696.9790231546224</v>
+        <v>910.1065830648117</v>
       </c>
       <c r="G24" t="n">
         <v>1400</v>
       </c>
       <c r="H24" t="n">
-        <v>12314.08487308269</v>
+        <v>11844.81701068009</v>
       </c>
       <c r="I24" t="n">
-        <v>433.3461568376058</v>
+        <v>420.2131661296235</v>
       </c>
       <c r="J24" t="n">
-        <v>1355.9</v>
+        <v>1321.6</v>
       </c>
       <c r="K24" t="n">
-        <v>0.4000000000000004</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>288</v>
+        <v>265.5</v>
       </c>
       <c r="B25" t="n">
-        <v>103.6</v>
+        <v>122</v>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E25" t="n">
-        <v>12256.11328493796</v>
+        <v>11961.71196128481</v>
       </c>
       <c r="F25" t="n">
-        <v>611.7643592945767</v>
+        <v>913.5043411382335</v>
       </c>
       <c r="G25" t="n">
         <v>1400</v>
       </c>
       <c r="H25" t="n">
-        <v>12320.14160617244</v>
+        <v>11923.42392256962</v>
       </c>
       <c r="I25" t="n">
-        <v>414.7054491182209</v>
+        <v>427.008682276467</v>
       </c>
       <c r="J25" t="n">
-        <v>1380.4</v>
+        <v>1321.6</v>
       </c>
       <c r="K25" t="n">
-        <v>3.800000000000001</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="B26" t="n">
-        <v>117.6</v>
+        <v>140</v>
       </c>
       <c r="C26" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>12290.72318830795</v>
+        <v>12000</v>
       </c>
       <c r="F26" t="n">
-        <v>505.2460294695195</v>
+        <v>840</v>
       </c>
       <c r="G26" t="n">
         <v>1400</v>
       </c>
       <c r="H26" t="n">
-        <v>12327.06358684645</v>
+        <v>12000</v>
       </c>
       <c r="I26" t="n">
-        <v>393.4017831532094</v>
+        <v>420</v>
       </c>
       <c r="J26" t="n">
-        <v>1395.1</v>
+        <v>1355.9</v>
       </c>
       <c r="K26" t="n">
-        <v>3.099999999999998</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>288</v>
+        <v>274.5</v>
       </c>
       <c r="B27" t="n">
-        <v>131.6</v>
+        <v>102</v>
       </c>
       <c r="C27" t="n">
         <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>12325.33309167795</v>
+        <v>12064.02262211392</v>
       </c>
       <c r="F27" t="n">
-        <v>398.7276996444623</v>
+        <v>586.5154556737676</v>
       </c>
       <c r="G27" t="n">
         <v>1400</v>
       </c>
       <c r="H27" t="n">
-        <v>12325.33309167795</v>
+        <v>12080.0282776424</v>
       </c>
       <c r="I27" t="n">
-        <v>398.7276996444623</v>
+        <v>383.1443195922095</v>
       </c>
       <c r="J27" t="n">
-        <v>1400</v>
+        <v>1380.4</v>
       </c>
       <c r="K27" t="n">
-        <v>3.699999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>297</v>
+        <v>274.5</v>
       </c>
       <c r="B28" t="n">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="C28" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>12508.46935970829</v>
+        <v>12043.93709360759</v>
       </c>
       <c r="F28" t="n">
-        <v>402.0726929090279</v>
+        <v>841.7262931094483</v>
       </c>
       <c r="G28" t="n">
         <v>1400</v>
       </c>
       <c r="H28" t="n">
-        <v>12508.46935970829</v>
+        <v>12076.88991381329</v>
       </c>
       <c r="I28" t="n">
-        <v>402.0726929090279</v>
+        <v>423.0210129415345</v>
       </c>
       <c r="J28" t="n">
-        <v>1400</v>
+        <v>1355.9</v>
       </c>
       <c r="K28" t="n">
-        <v>2.900000000000002</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B29" t="n">
-        <v>78.40000000000001</v>
+        <v>102</v>
       </c>
       <c r="C29" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D29" t="n">
         <v>2</v>
       </c>
       <c r="E29" t="n">
-        <v>12427.11426215497</v>
+        <v>12127.65052347283</v>
       </c>
       <c r="F29" t="n">
-        <v>561.7410620435833</v>
+        <v>594.0463140743676</v>
       </c>
       <c r="G29" t="n">
         <v>1400</v>
       </c>
       <c r="H29" t="n">
-        <v>12498.29997251413</v>
+        <v>12159.56315434103</v>
       </c>
       <c r="I29" t="n">
-        <v>422.0312390508471</v>
+        <v>392.5578925929595</v>
       </c>
       <c r="J29" t="n">
         <v>1380.4</v>
       </c>
       <c r="K29" t="n">
-        <v>2.199999999999999</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>297</v>
+        <v>279</v>
       </c>
       <c r="B30" t="n">
-        <v>84</v>
+        <v>140</v>
       </c>
       <c r="C30" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>12457.62242373746</v>
+        <v>12087.60330042253</v>
       </c>
       <c r="F30" t="n">
-        <v>501.8654236181251</v>
+        <v>846.8945292667229</v>
       </c>
       <c r="G30" t="n">
         <v>1400</v>
       </c>
       <c r="H30" t="n">
-        <v>12495.75762571559</v>
+        <v>12153.30577573943</v>
       </c>
       <c r="I30" t="n">
-        <v>427.0208755863022</v>
+        <v>432.065426216765</v>
       </c>
       <c r="J30" t="n">
-        <v>1395.1</v>
+        <v>1355.9</v>
       </c>
       <c r="K30" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>297</v>
+        <v>283.5</v>
       </c>
       <c r="B31" t="n">
-        <v>92.40000000000001</v>
+        <v>102</v>
       </c>
       <c r="C31" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>12503.38466611121</v>
+        <v>12190.49141690642</v>
       </c>
       <c r="F31" t="n">
-        <v>412.0519659799374</v>
+        <v>606.5461449554959</v>
       </c>
       <c r="G31" t="n">
         <v>1400</v>
       </c>
       <c r="H31" t="n">
-        <v>12503.38466611121</v>
+        <v>12238.11427113302</v>
       </c>
       <c r="I31" t="n">
-        <v>412.0519659799374</v>
+        <v>408.1826811943699</v>
       </c>
       <c r="J31" t="n">
-        <v>1400</v>
+        <v>1380.4</v>
       </c>
       <c r="K31" t="n">
-        <v>3.800000000000001</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>297</v>
+        <v>283.5</v>
       </c>
       <c r="B32" t="n">
-        <v>120.4</v>
+        <v>104</v>
       </c>
       <c r="C32" t="n">
         <v>8</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
-        <v>12437.28364934913</v>
+        <v>12194.22654272811</v>
       </c>
       <c r="F32" t="n">
-        <v>541.7825159017639</v>
+        <v>590.9882262291331</v>
       </c>
       <c r="G32" t="n">
         <v>1400</v>
       </c>
       <c r="H32" t="n">
-        <v>12491.94410551777</v>
+        <v>12242.78317841014</v>
       </c>
       <c r="I32" t="n">
-        <v>434.5053303894844</v>
+        <v>388.7352827864164</v>
       </c>
       <c r="J32" t="n">
-        <v>1395.1</v>
+        <v>1380.4</v>
       </c>
       <c r="K32" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>297</v>
+        <v>283.5</v>
       </c>
       <c r="B33" t="n">
-        <v>137.2</v>
+        <v>114</v>
       </c>
       <c r="C33" t="n">
         <v>8</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>12498.29997251413</v>
+        <v>12212.90217183659</v>
       </c>
       <c r="F33" t="n">
-        <v>422.0312390508474</v>
+        <v>513.198632597319</v>
       </c>
       <c r="G33" t="n">
         <v>1400</v>
       </c>
       <c r="H33" t="n">
-        <v>12498.29997251413</v>
+        <v>12239.51494331616</v>
       </c>
       <c r="I33" t="n">
-        <v>422.0312390508474</v>
+        <v>402.3484616719839</v>
       </c>
       <c r="J33" t="n">
-        <v>1400</v>
+        <v>1395.1</v>
       </c>
       <c r="K33" t="n">
-        <v>3.699999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>306</v>
+        <v>283.5</v>
       </c>
       <c r="B34" t="n">
-        <v>75.59999999999999</v>
+        <v>116</v>
       </c>
       <c r="C34" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>12216.63729765828</v>
+      </c>
+      <c r="F34" t="n">
+        <v>497.6407138709561</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H34" t="n">
+        <v>12243.71695986557</v>
+      </c>
+      <c r="I34" t="n">
+        <v>384.8458031048256</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1395.1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>283.5</v>
+      </c>
+      <c r="B35" t="n">
+        <v>130</v>
+      </c>
+      <c r="C35" t="n">
+        <v>8</v>
+      </c>
+      <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="n">
-        <v>12710.98504117297</v>
-      </c>
-      <c r="F34" t="n">
-        <v>421.4130436040635</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1400</v>
-      </c>
-      <c r="H34" t="n">
-        <v>12710.98504117297</v>
-      </c>
-      <c r="I34" t="n">
-        <v>421.4130436040635</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1400</v>
-      </c>
-      <c r="K34" t="n">
-        <v>1.100000000000001</v>
+      <c r="E35" t="n">
+        <v>12242.78317841014</v>
+      </c>
+      <c r="F35" t="n">
+        <v>388.7352827864164</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H35" t="n">
+        <v>12242.78317841014</v>
+      </c>
+      <c r="I35" t="n">
+        <v>388.7352827864164</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1400</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>283.5</v>
+      </c>
+      <c r="B36" t="n">
+        <v>140</v>
+      </c>
+      <c r="C36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>12130.72940375931</v>
+      </c>
+      <c r="F36" t="n">
+        <v>855.4728445773011</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H36" t="n">
+        <v>12228.77645657879</v>
+      </c>
+      <c r="I36" t="n">
+        <v>447.0774780102769</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1355.9</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>288</v>
+      </c>
+      <c r="B37" t="n">
+        <v>104</v>
+      </c>
+      <c r="C37" t="n">
+        <v>8</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>12257.10213931996</v>
+      </c>
+      <c r="F37" t="n">
+        <v>608.7209784424322</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H37" t="n">
+        <v>12321.37767414994</v>
+      </c>
+      <c r="I37" t="n">
+        <v>410.9012230530402</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1380.4</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>288</v>
+      </c>
+      <c r="B38" t="n">
+        <v>116</v>
+      </c>
+      <c r="C38" t="n">
+        <v>8</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>12286.76777077995</v>
+      </c>
+      <c r="F38" t="n">
+        <v>517.4195528780974</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H38" t="n">
+        <v>12322.61374212744</v>
+      </c>
+      <c r="I38" t="n">
+        <v>407.0969969878596</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1395.1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>288</v>
+      </c>
+      <c r="B39" t="n">
+        <v>118</v>
+      </c>
+      <c r="C39" t="n">
+        <v>8</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>12291.71204268995</v>
+      </c>
+      <c r="F39" t="n">
+        <v>502.202648617375</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H39" t="n">
+        <v>12328.17604802619</v>
+      </c>
+      <c r="I39" t="n">
+        <v>389.9779796945468</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1395.1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>288</v>
+      </c>
+      <c r="B40" t="n">
+        <v>130</v>
+      </c>
+      <c r="C40" t="n">
+        <v>8</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>12321.37767414995</v>
+      </c>
+      <c r="F40" t="n">
+        <v>410.9012230530402</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H40" t="n">
+        <v>12321.37767414995</v>
+      </c>
+      <c r="I40" t="n">
+        <v>410.9012230530402</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1400</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>288</v>
+      </c>
+      <c r="B41" t="n">
+        <v>132</v>
+      </c>
+      <c r="C41" t="n">
+        <v>8</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>12326.32194605994</v>
+      </c>
+      <c r="F41" t="n">
+        <v>395.6843187923178</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H41" t="n">
+        <v>12326.32194605994</v>
+      </c>
+      <c r="I41" t="n">
+        <v>395.6843187923178</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1400</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="B42" t="n">
+        <v>104</v>
+      </c>
+      <c r="C42" t="n">
+        <v>8</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="n">
+        <v>12318.39261572775</v>
+      </c>
+      <c r="F42" t="n">
+        <v>631.3322289506095</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H42" t="n">
+        <v>12397.99076965969</v>
+      </c>
+      <c r="I42" t="n">
+        <v>439.1652861882619</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1380.4</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="B43" t="n">
+        <v>106</v>
+      </c>
+      <c r="C43" t="n">
+        <v>8</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" t="n">
+        <v>12324.5155506456</v>
+      </c>
+      <c r="F43" t="n">
+        <v>616.550156430429</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H43" t="n">
+        <v>12405.644438307</v>
+      </c>
+      <c r="I43" t="n">
+        <v>420.6876955380362</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1380.4</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="B44" t="n">
+        <v>118</v>
+      </c>
+      <c r="C44" t="n">
+        <v>8</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>12361.25316015264</v>
+      </c>
+      <c r="F44" t="n">
+        <v>527.8577213093454</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H44" t="n">
+        <v>12406.40980517172</v>
+      </c>
+      <c r="I44" t="n">
+        <v>418.8399364730136</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1395.1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="B45" t="n">
+        <v>120</v>
+      </c>
+      <c r="C45" t="n">
+        <v>8</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>12367.37609507049</v>
+      </c>
+      <c r="F45" t="n">
+        <v>513.0756487891648</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H45" t="n">
+        <v>12413.2981069543</v>
+      </c>
+      <c r="I45" t="n">
+        <v>402.2101048878104</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1395.1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="B46" t="n">
+        <v>132</v>
+      </c>
+      <c r="C46" t="n">
+        <v>8</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>12404.11370457754</v>
+      </c>
+      <c r="F46" t="n">
+        <v>424.3832136680813</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H46" t="n">
+        <v>12404.11370457754</v>
+      </c>
+      <c r="I46" t="n">
+        <v>424.3832136680813</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1400</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>292.5</v>
+      </c>
+      <c r="B47" t="n">
+        <v>134</v>
+      </c>
+      <c r="C47" t="n">
+        <v>8</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="n">
+        <v>12410.23663949538</v>
+      </c>
+      <c r="F47" t="n">
+        <v>409.6011411479008</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H47" t="n">
+        <v>12410.23663949538</v>
+      </c>
+      <c r="I47" t="n">
+        <v>409.6011411479008</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1400</v>
+      </c>
+      <c r="K47" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>297</v>
+      </c>
+      <c r="B48" t="n">
+        <v>108</v>
+      </c>
+      <c r="C48" t="n">
+        <v>8</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" t="n">
+        <v>12392.24779177497</v>
+      </c>
+      <c r="F48" t="n">
+        <v>630.17036310125</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H48" t="n">
+        <v>12490.30973971871</v>
+      </c>
+      <c r="I48" t="n">
+        <v>437.7129538765626</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1380.4</v>
+      </c>
+      <c r="K48" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>297</v>
+      </c>
+      <c r="B49" t="n">
+        <v>120</v>
+      </c>
+      <c r="C49" t="n">
+        <v>8</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>12435.83087974996</v>
+      </c>
+      <c r="F49" t="n">
+        <v>544.6337367791667</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H49" t="n">
+        <v>12490.30973971871</v>
+      </c>
+      <c r="I49" t="n">
+        <v>437.7129538765626</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1395.1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>297</v>
+      </c>
+      <c r="B50" t="n">
+        <v>122</v>
+      </c>
+      <c r="C50" t="n">
+        <v>8</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>12443.0947277458</v>
+      </c>
+      <c r="F50" t="n">
+        <v>530.3776323921528</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H50" t="n">
+        <v>12498.48156871402</v>
+      </c>
+      <c r="I50" t="n">
+        <v>421.6748364411719</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1395.1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>297</v>
+      </c>
+      <c r="B51" t="n">
+        <v>136</v>
+      </c>
+      <c r="C51" t="n">
+        <v>8</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>12493.94166371663</v>
+      </c>
+      <c r="F51" t="n">
+        <v>430.5849016830556</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H51" t="n">
+        <v>12493.94166371663</v>
+      </c>
+      <c r="I51" t="n">
+        <v>430.5849016830556</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1400</v>
+      </c>
+      <c r="K51" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>297</v>
+      </c>
+      <c r="B52" t="n">
+        <v>138</v>
+      </c>
+      <c r="C52" t="n">
+        <v>8</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="n">
+        <v>12501.20551171246</v>
+      </c>
+      <c r="F52" t="n">
+        <v>416.3287972960417</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H52" t="n">
+        <v>12501.20551171246</v>
+      </c>
+      <c r="I52" t="n">
+        <v>416.3287972960417</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1400</v>
+      </c>
+      <c r="K52" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>301.5</v>
+      </c>
+      <c r="B53" t="n">
+        <v>124</v>
+      </c>
+      <c r="C53" t="n">
+        <v>8</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>12518.31857619822</v>
+      </c>
+      <c r="F53" t="n">
+        <v>554.1809569607407</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H53" t="n">
+        <v>12583.108398223</v>
+      </c>
+      <c r="I53" t="n">
+        <v>448.4535765808333</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1395.1</v>
+      </c>
+      <c r="K53" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>301.5</v>
+      </c>
+      <c r="B54" t="n">
+        <v>126</v>
+      </c>
+      <c r="C54" t="n">
+        <v>8</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>12526.67855323368</v>
+      </c>
+      <c r="F54" t="n">
+        <v>540.5387143310752</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H54" t="n">
+        <v>12592.51337238789</v>
+      </c>
+      <c r="I54" t="n">
+        <v>433.1060536224596</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1395.1</v>
+      </c>
+      <c r="K54" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>301.5</v>
+      </c>
+      <c r="B55" t="n">
+        <v>140</v>
+      </c>
+      <c r="C55" t="n">
+        <v>8</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>12585.19839248186</v>
+      </c>
+      <c r="F55" t="n">
+        <v>445.0430159234169</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1400</v>
+      </c>
+      <c r="H55" t="n">
+        <v>12585.19839248186</v>
+      </c>
+      <c r="I55" t="n">
+        <v>445.0430159234169</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1400</v>
+      </c>
+      <c r="K55" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
